--- a/output/StructureDefinition-BRRequisicaoRegulacaoAssistencial.xlsx
+++ b/output/StructureDefinition-BRRequisicaoRegulacaoAssistencial.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4734" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4733" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -54,67 +54,67 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2023-04-04</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Ministério da Saúde do Brasil</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>ServiceRequest</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/ServiceRequest</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2023-04-04</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>Ministério da Saúde do Brasil</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>resource</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>ServiceRequest</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ServiceRequest</t>
-  </si>
-  <si>
-    <t>Abstract</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}mira-1:O Motivo da Solicitação (Condition.code) deve ser preenchido caso a Data da Solicitação (ServiceRequest.authoredOn) seja posterior a 01/01/2025. {(authoredOn &gt; @2025-01-01T01:00:00) implies reasonReference.resolve().code.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -283,9 +283,6 @@
   </si>
   <si>
     <t>ServiceRequest.id</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>Y</t>
@@ -307,6 +304,9 @@
     <t>Resource.id</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>ServiceRequest.meta</t>
   </si>
   <si>
@@ -638,6 +638,10 @@
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRStatusRequisicaoRegulacaoAssistencial</t>
   </si>
   <si>
+    <t>mira-13
+mira-14mira-15mira-16mira-17mira-18mira-19</t>
+  </si>
+  <si>
     <t>Request.status</t>
   </si>
   <si>
@@ -656,13 +660,16 @@
     <t>ServiceRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>proposal | plan |  directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
+  </si>
+  <si>
+    <t>proposal</t>
   </si>
   <si>
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRIntencaoRegulacao</t>
@@ -684,16 +691,19 @@
 </t>
   </si>
   <si>
+    <t>Modalidade assistencial</t>
+  </si>
+  <si>
+    <t>Modalidade assistencial que gerou a solicitação do procedimento.</t>
+  </si>
+  <si>
+    <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what service request are retrieved and displayed.</t>
+  </si>
+  <si>
     <t>Modalidade assistencial.</t>
-  </si>
-  <si>
-    <t>A code that classifies the service for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
-  </si>
-  <si>
-    <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
     <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRModalidadeAssistencialMIRA</t>
@@ -919,10 +929,7 @@
     <t>ServiceRequest.priority</t>
   </si>
   <si>
-    <t>Caráter do atendimento.</t>
-  </si>
-  <si>
-    <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
+    <t>Caráter da solicitação</t>
   </si>
   <si>
     <t>If missing, this task should be performed with normal priority</t>
@@ -977,10 +984,10 @@
 </t>
   </si>
   <si>
-    <t>Código do procedimento.</t>
-  </si>
-  <si>
-    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+    <t>Código do procedimento</t>
+  </si>
+  <si>
+    <t>O código que identifica unicamente o procedimento conforme tabela SUS.</t>
   </si>
   <si>
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
@@ -1098,10 +1105,10 @@
 </t>
   </si>
   <si>
-    <t>Paciente</t>
-  </si>
-  <si>
-    <t>On whom or what the service is to be performed. This is usually a human patient, but can also be requested on animals, groups of humans or animals, devices such as dialysis machines, or even locations (typically for environmental scans).</t>
+    <t>Identificador do paciente</t>
+  </si>
+  <si>
+    <t>Identificação única do paciente, por meio de CPF ou CNS.</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1187,6 +1194,10 @@
     <t>Reference.identifier</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ident-1:O número de CPF ou CNS informado é inválido (subject.identifier.value). {value.matches('^(?!(\\d)\\1{10})\\d{11}$') or value.matches('^(?!(\\d)\\1{14})[125789]\\d{14}$')}</t>
+  </si>
+  <si>
     <t>ServiceRequest.subject.identifier.id</t>
   </si>
   <si>
@@ -1403,10 +1414,14 @@
 </t>
   </si>
   <si>
-    <t>Data de execução</t>
-  </si>
-  <si>
-    <t>Data e hora da execução do procedimento no padrão ISO8601.</t>
+    <t>Data da execução</t>
+  </si>
+  <si>
+    <t>A data e hora em que o procedimento regulado foi executado no padrão ISO 8601.</t>
+  </si>
+  <si>
+    <t>mira-3
+mira-9mira-12</t>
   </si>
   <si>
     <t>Request.occurrence[x]</t>
@@ -1480,10 +1495,14 @@
 </t>
   </si>
   <si>
-    <t>Data e hora em que o procediento foi solicitado.</t>
-  </si>
-  <si>
-    <t>Data e hora da solicitação do procedimento no padrão ISO8601.</t>
+    <t>Data da solicitação</t>
+  </si>
+  <si>
+    <t>A data e hora da solicitação do procedimento regulado no padrão ISO 8601.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mira-1
+</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -1515,7 +1534,7 @@
     <t>Estabelecimento de saúde solicitante</t>
   </si>
   <si>
-    <t>The individual who initiated the request and has responsibility for its activation.</t>
+    <t>Identificação única do estabelecimento solicitante, por meio do CNES.</t>
   </si>
   <si>
     <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
@@ -1549,6 +1568,10 @@
   </si>
   <si>
     <t>ServiceRequest.requester.identifier</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+estab-2:O número do CNES do estabelecimento de saúde é inválido (identifier.value). O número deve conter 7 dígitos e não pode conter letras ou caracteres especiais, apenas números. {value.matches('^(?!(\\d)\\1{6})\\d{7}$')}</t>
   </si>
   <si>
     <t>ServiceRequest.requester.identifier.id</t>
@@ -1585,10 +1608,11 @@
 </t>
   </si>
   <si>
-    <t>Identificador da especialidade médica do executante.</t>
-  </si>
-  <si>
-    <t>Desired type of performer for doing the requested service.</t>
+    <t>Especialidade médica do executante</t>
+  </si>
+  <si>
+    <t>Identificação da especialidade médica do profissional executante do procedimento, conforme tabela de CBO. 
+Caso o procedimento informado pertença à forma de organização 03.01.01 da tabela SUS, o código CBO será obrigatório.</t>
   </si>
   <si>
     <t>This is a  role, not  a participation type.  In other words, does not describe the task but describes the capacity.  For example, “compounding pharmacy”, “psychiatrist” or “internal referral”.</t>
@@ -1652,13 +1676,17 @@
 </t>
   </si>
   <si>
-    <t>Estabelecimento de sáude executante</t>
-  </si>
-  <si>
-    <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
+    <t>Estabelecimento de saúde executante</t>
+  </si>
+  <si>
+    <t>Identificação única do estabelecimento executante, por meio do CNES.</t>
   </si>
   <si>
     <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+  </si>
+  <si>
+    <t>mira-4
+mira-6mira-8mira-11</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1776,14 +1804,14 @@
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/BRCID10Avaliado-1.0)
+    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/BRProblemaDiagnostico)
 </t>
   </si>
   <si>
     <t>Motivo da solicitação</t>
   </si>
   <si>
-    <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
+    <t>Identificação do motivo da solicitação do procedimento, conforme Classificação Internacional de Doenças - CID ou Classificação Internacional de Atenção Primária - CIAP.</t>
   </si>
   <si>
     <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
@@ -2165,45 +2193,43 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>9</v>
@@ -2211,54 +2237,54 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2448,10 +2474,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2531,7 +2557,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>
@@ -2577,28 +2603,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2648,13 +2674,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH3" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2694,16 +2720,16 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>97</v>
@@ -2769,7 +2795,7 @@
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>80</v>
@@ -2815,10 +2841,10 @@
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>103</v>
@@ -2886,7 +2912,7 @@
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
@@ -3003,7 +3029,7 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
@@ -3043,7 +3069,7 @@
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -3120,7 +3146,7 @@
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>80</v>
@@ -3400,7 +3426,7 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
@@ -3522,7 +3548,7 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>147</v>
@@ -3639,7 +3665,7 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>157</v>
@@ -3756,7 +3782,7 @@
         <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>103</v>
@@ -3873,7 +3899,7 @@
         <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>171</v>
@@ -3988,7 +4014,7 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>179</v>
@@ -4103,7 +4129,7 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>147</v>
@@ -4173,7 +4199,7 @@
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -4210,19 +4236,19 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="J17" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>109</v>
@@ -4285,39 +4311,39 @@
         <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4325,31 +4351,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="J18" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4357,7 +4383,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>80</v>
@@ -4379,7 +4405,7 @@
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -4397,13 +4423,13 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
@@ -4412,16 +4438,16 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
@@ -4429,10 +4455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4440,34 +4466,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4495,28 +4521,28 @@
         <v>198</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4534,13 +4560,13 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -4548,10 +4574,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4574,13 +4600,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4631,13 +4657,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -4652,7 +4678,7 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -4663,10 +4689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4695,7 +4721,7 @@
         <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>138</v>
@@ -4736,19 +4762,19 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4769,7 +4795,7 @@
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
@@ -4780,10 +4806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4791,34 +4817,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4867,7 +4893,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4885,10 +4911,10 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4899,10 +4925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4925,13 +4951,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4982,13 +5008,13 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
@@ -5003,7 +5029,7 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -5014,10 +5040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5046,7 +5072,7 @@
         <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>138</v>
@@ -5087,19 +5113,19 @@
         <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5120,7 +5146,7 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
@@ -5131,10 +5157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5142,34 +5168,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5218,13 +5244,13 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
@@ -5236,10 +5262,10 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -5250,10 +5276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5264,28 +5290,28 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5335,13 +5361,13 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
@@ -5353,10 +5379,10 @@
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
@@ -5367,10 +5393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5378,32 +5404,32 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5452,13 +5478,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
@@ -5470,10 +5496,10 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -5484,10 +5510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5498,29 +5524,29 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5569,13 +5595,13 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
@@ -5587,10 +5613,10 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -5601,10 +5627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5624,22 +5650,22 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5688,13 +5714,13 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
@@ -5706,10 +5732,10 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5720,10 +5746,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5743,22 +5769,22 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5807,13 +5833,13 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
@@ -5825,10 +5851,10 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5839,10 +5865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5850,28 +5876,28 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5879,7 +5905,7 @@
         <v>80</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>80</v>
@@ -5903,10 +5929,10 @@
         <v>198</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5924,13 +5950,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5939,16 +5965,16 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5956,10 +5982,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5976,82 +6002,82 @@
         <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="R32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q32" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="R32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
@@ -6060,13 +6086,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -6077,42 +6103,42 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6141,10 +6167,10 @@
         <v>198</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -6162,13 +6188,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -6177,27 +6203,27 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6220,13 +6246,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6277,13 +6303,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -6298,7 +6324,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -6309,10 +6335,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6341,7 +6367,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>138</v>
@@ -6382,19 +6408,19 @@
         <v>80</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6415,7 +6441,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6426,10 +6452,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6437,34 +6463,34 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6513,7 +6539,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6531,10 +6557,10 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6545,10 +6571,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6571,13 +6597,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6628,13 +6654,13 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
@@ -6649,7 +6675,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -6660,10 +6686,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6692,7 +6718,7 @@
         <v>136</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>138</v>
@@ -6733,19 +6759,19 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6766,7 +6792,7 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6777,10 +6803,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6788,34 +6814,34 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J39" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6864,13 +6890,13 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
@@ -6882,10 +6908,10 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6896,10 +6922,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6910,28 +6936,28 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6981,13 +7007,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
@@ -6999,10 +7025,10 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -7013,10 +7039,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7024,32 +7050,32 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7098,13 +7124,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -7116,10 +7142,10 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7130,10 +7156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7144,29 +7170,29 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K42" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7215,13 +7241,13 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
@@ -7233,10 +7259,10 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -7247,10 +7273,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7270,22 +7296,22 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7334,13 +7360,13 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
@@ -7352,10 +7378,10 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7366,10 +7392,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7389,22 +7415,22 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7453,13 +7479,13 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
@@ -7471,10 +7497,10 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7485,14 +7511,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7508,19 +7534,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7546,13 +7572,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7570,7 +7596,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7579,7 +7605,7 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>101</v>
@@ -7588,24 +7614,24 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7625,20 +7651,20 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7687,13 +7713,13 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
@@ -7705,10 +7731,10 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7719,10 +7745,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7730,28 +7756,28 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7802,13 +7828,13 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
@@ -7817,27 +7843,27 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7860,13 +7886,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7917,13 +7943,13 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
@@ -7938,7 +7964,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7949,10 +7975,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7981,7 +8007,7 @@
         <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -8022,19 +8048,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8055,7 +8081,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8066,10 +8092,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8089,19 +8115,19 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8151,16 +8177,16 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
@@ -8183,10 +8209,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8206,19 +8232,19 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8244,13 +8270,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8268,13 +8294,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -8300,10 +8326,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8311,31 +8337,31 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>147</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8385,19 +8411,19 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>380</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -8417,10 +8443,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8443,13 +8469,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8500,13 +8526,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8521,7 +8547,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8532,10 +8558,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8564,7 +8590,7 @@
         <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>138</v>
@@ -8605,19 +8631,19 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8638,7 +8664,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8649,10 +8675,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8669,25 +8695,25 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8715,10 +8741,10 @@
         <v>198</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8736,13 +8762,13 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
@@ -8757,7 +8783,7 @@
         <v>132</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8768,10 +8794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8791,22 +8817,22 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8831,13 +8857,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8855,13 +8881,13 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
@@ -8873,10 +8899,10 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8887,10 +8913,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8898,34 +8924,34 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8938,7 +8964,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>80</v>
@@ -8974,13 +9000,13 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
@@ -8992,10 +9018,10 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9006,10 +9032,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9017,31 +9043,31 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9055,7 +9081,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>80</v>
@@ -9091,13 +9117,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -9109,10 +9135,10 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -9123,10 +9149,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9146,16 +9172,16 @@
         <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9206,13 +9232,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -9224,10 +9250,10 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9238,10 +9264,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9261,19 +9287,19 @@
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9323,13 +9349,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9341,10 +9367,10 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -9355,10 +9381,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9378,19 +9404,19 @@
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9440,13 +9466,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -9472,14 +9498,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9495,16 +9521,16 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9555,13 +9581,13 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
@@ -9570,56 +9596,56 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9670,42 +9696,42 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9728,13 +9754,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9785,13 +9811,13 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
@@ -9817,10 +9843,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9902,7 +9928,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9934,10 +9960,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9948,7 +9974,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -9960,13 +9986,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10017,13 +10043,13 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
@@ -10049,10 +10075,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10072,16 +10098,16 @@
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10108,37 +10134,37 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
@@ -10153,50 +10179,50 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K68" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10247,74 +10273,74 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>80</v>
+        <v>479</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K69" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10364,13 +10390,13 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
@@ -10379,27 +10405,27 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10422,13 +10448,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10479,13 +10505,13 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
@@ -10500,7 +10526,7 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>80</v>
@@ -10511,10 +10537,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10543,7 +10569,7 @@
         <v>136</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>138</v>
@@ -10584,19 +10610,19 @@
         <v>80</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10617,7 +10643,7 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>80</v>
@@ -10628,10 +10654,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10651,19 +10677,19 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10713,16 +10739,16 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>101</v>
@@ -10745,10 +10771,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10768,19 +10794,19 @@
         <v>80</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10806,13 +10832,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10830,13 +10856,13 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>80</v>
@@ -10862,10 +10888,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10873,31 +10899,31 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>147</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10947,19 +10973,19 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
@@ -10979,10 +11005,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11005,13 +11031,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11062,13 +11088,13 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>80</v>
@@ -11083,7 +11109,7 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>80</v>
@@ -11094,10 +11120,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11126,7 +11152,7 @@
         <v>136</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>138</v>
@@ -11167,19 +11193,19 @@
         <v>80</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11200,7 +11226,7 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>80</v>
@@ -11211,10 +11237,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11231,25 +11257,25 @@
         <v>80</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11277,10 +11303,10 @@
         <v>198</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11298,13 +11324,13 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
@@ -11319,7 +11345,7 @@
         <v>132</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>80</v>
@@ -11330,10 +11356,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11353,22 +11379,22 @@
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11393,13 +11419,13 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>80</v>
@@ -11417,13 +11443,13 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
@@ -11435,10 +11461,10 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>80</v>
@@ -11449,10 +11475,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11460,34 +11486,34 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J79" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11500,7 +11526,7 @@
         <v>80</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>80</v>
@@ -11536,13 +11562,13 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
@@ -11554,10 +11580,10 @@
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>80</v>
@@ -11568,10 +11594,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11579,31 +11605,31 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J80" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K80" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11617,7 +11643,7 @@
         <v>80</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>80</v>
@@ -11653,13 +11679,13 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
@@ -11671,10 +11697,10 @@
         <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>80</v>
@@ -11685,10 +11711,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11708,16 +11734,16 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11768,13 +11794,13 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
@@ -11786,10 +11812,10 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>80</v>
@@ -11800,10 +11826,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11823,19 +11849,19 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11885,13 +11911,13 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
@@ -11903,10 +11929,10 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>80</v>
@@ -11917,10 +11943,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11940,19 +11966,19 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12002,13 +12028,13 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
@@ -12034,42 +12060,42 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J84" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K84" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12098,34 +12124,34 @@
         <v>198</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="Z84" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AA84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
@@ -12134,16 +12160,16 @@
         <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12151,10 +12177,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12177,13 +12203,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12234,13 +12260,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
@@ -12255,7 +12281,7 @@
         <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>80</v>
@@ -12266,10 +12292,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12298,7 +12324,7 @@
         <v>136</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>138</v>
@@ -12339,19 +12365,19 @@
         <v>80</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12372,7 +12398,7 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>80</v>
@@ -12383,10 +12409,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12394,34 +12420,34 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K87" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12470,7 +12496,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12488,10 +12514,10 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>80</v>
@@ -12502,10 +12528,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12528,13 +12554,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12585,13 +12611,13 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>80</v>
@@ -12606,7 +12632,7 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>80</v>
@@ -12617,10 +12643,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12649,7 +12675,7 @@
         <v>136</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>138</v>
@@ -12690,19 +12716,19 @@
         <v>80</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12723,7 +12749,7 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>80</v>
@@ -12734,10 +12760,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12745,34 +12771,34 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J90" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -12821,13 +12847,13 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>80</v>
@@ -12839,10 +12865,10 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>80</v>
@@ -12853,10 +12879,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12867,28 +12893,28 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J91" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K91" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12938,13 +12964,13 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>80</v>
@@ -12956,10 +12982,10 @@
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>80</v>
@@ -12970,10 +12996,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12981,32 +13007,32 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13055,13 +13081,13 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
@@ -13073,10 +13099,10 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>80</v>
@@ -13087,10 +13113,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13101,29 +13127,29 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K93" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13172,13 +13198,13 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
@@ -13190,10 +13216,10 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>80</v>
@@ -13204,10 +13230,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13227,22 +13253,22 @@
         <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13291,13 +13317,13 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
@@ -13309,10 +13335,10 @@
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>80</v>
@@ -13323,10 +13349,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13346,22 +13372,22 @@
         <v>80</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -13410,13 +13436,13 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>80</v>
@@ -13428,10 +13454,10 @@
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>80</v>
@@ -13442,42 +13468,42 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K96" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13527,7 +13553,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13536,22 +13562,22 @@
         <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>80</v>
+        <v>538</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -13559,10 +13585,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13585,13 +13611,13 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13642,13 +13668,13 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
@@ -13663,7 +13689,7 @@
         <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>80</v>
@@ -13674,10 +13700,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13706,7 +13732,7 @@
         <v>136</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>138</v>
@@ -13747,19 +13773,19 @@
         <v>80</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13780,7 +13806,7 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>80</v>
@@ -13791,10 +13817,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13814,19 +13840,19 @@
         <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13876,16 +13902,16 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>101</v>
@@ -13908,10 +13934,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13931,19 +13957,19 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13969,13 +13995,13 @@
         <v>80</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -13993,13 +14019,13 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>80</v>
@@ -14025,10 +14051,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14036,31 +14062,31 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J101" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>147</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14110,19 +14136,19 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>80</v>
@@ -14142,10 +14168,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14168,13 +14194,13 @@
         <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14225,13 +14251,13 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>80</v>
@@ -14246,7 +14272,7 @@
         <v>80</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>80</v>
@@ -14257,10 +14283,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14289,7 +14315,7 @@
         <v>136</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>138</v>
@@ -14330,19 +14356,19 @@
         <v>80</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14363,7 +14389,7 @@
         <v>80</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>80</v>
@@ -14374,10 +14400,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14394,25 +14420,25 @@
         <v>80</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14440,10 +14466,10 @@
         <v>198</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>80</v>
@@ -14461,13 +14487,13 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>80</v>
@@ -14482,7 +14508,7 @@
         <v>132</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>80</v>
@@ -14493,10 +14519,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14516,22 +14542,22 @@
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -14556,13 +14582,13 @@
         <v>80</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>80</v>
@@ -14580,13 +14606,13 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>80</v>
@@ -14598,10 +14624,10 @@
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>80</v>
@@ -14612,10 +14638,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14623,34 +14649,34 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J106" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -14663,7 +14689,7 @@
         <v>80</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>80</v>
@@ -14699,13 +14725,13 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>80</v>
@@ -14717,10 +14743,10 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>80</v>
@@ -14731,10 +14757,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14742,31 +14768,31 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J107" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K107" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14780,7 +14806,7 @@
         <v>80</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>80</v>
@@ -14816,13 +14842,13 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>80</v>
@@ -14834,10 +14860,10 @@
         <v>80</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>80</v>
@@ -14848,10 +14874,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14871,16 +14897,16 @@
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14931,13 +14957,13 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>80</v>
@@ -14949,10 +14975,10 @@
         <v>80</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>80</v>
@@ -14963,10 +14989,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14986,19 +15012,19 @@
         <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15048,13 +15074,13 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>80</v>
@@ -15066,10 +15092,10 @@
         <v>80</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>80</v>
@@ -15080,10 +15106,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15103,19 +15129,19 @@
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15165,13 +15191,13 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>80</v>
@@ -15197,10 +15223,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15220,16 +15246,16 @@
         <v>80</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15256,13 +15282,13 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -15280,7 +15306,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15301,10 +15327,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15312,10 +15338,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15335,16 +15361,16 @@
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15395,7 +15421,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15416,10 +15442,10 @@
         <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -15427,10 +15453,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15450,19 +15476,19 @@
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15488,13 +15514,13 @@
         <v>80</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -15512,7 +15538,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15527,16 +15553,16 @@
         <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -15544,10 +15570,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15555,31 +15581,31 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J114" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G114" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K114" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15629,7 +15655,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15644,16 +15670,16 @@
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -15661,10 +15687,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15687,13 +15713,13 @@
         <v>80</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15744,13 +15770,13 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>80</v>
@@ -15765,7 +15791,7 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>80</v>
@@ -15776,10 +15802,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15808,7 +15834,7 @@
         <v>136</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>138</v>
@@ -15849,19 +15875,19 @@
         <v>80</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15882,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>80</v>
@@ -15893,10 +15919,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15904,31 +15930,31 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J117" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G117" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K117" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15978,16 +16004,16 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>101</v>
@@ -16010,10 +16036,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16033,19 +16059,19 @@
         <v>80</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16071,13 +16097,13 @@
         <v>80</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>80</v>
@@ -16095,13 +16121,13 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>80</v>
@@ -16127,10 +16153,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16150,19 +16176,19 @@
         <v>80</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>147</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16212,13 +16238,13 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>80</v>
@@ -16244,10 +16270,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16267,19 +16293,19 @@
         <v>80</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16329,13 +16355,13 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>80</v>
@@ -16361,10 +16387,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16387,13 +16413,13 @@
         <v>80</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16444,7 +16470,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16459,13 +16485,13 @@
         <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>80</v>
@@ -16476,14 +16502,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16502,16 +16528,16 @@
         <v>80</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16561,7 +16587,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16576,13 +16602,13 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>80</v>
@@ -16593,10 +16619,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16616,19 +16642,19 @@
         <v>80</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16678,7 +16704,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16696,10 +16722,10 @@
         <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>80</v>
@@ -16710,14 +16736,14 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16733,22 +16759,22 @@
         <v>80</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -16773,31 +16799,31 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="Z124" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16815,24 +16841,24 @@
         <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16855,13 +16881,13 @@
         <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>49</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16912,7 +16938,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16927,27 +16953,27 @@
         <v>101</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16967,16 +16993,16 @@
         <v>80</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17027,13 +17053,13 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>80</v>
@@ -17045,10 +17071,10 @@
         <v>80</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>80</v>
@@ -17059,10 +17085,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17085,16 +17111,16 @@
         <v>80</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17144,7 +17170,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17159,13 +17185,13 @@
         <v>101</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>80</v>
